--- a/config/excel/DB抽出条件.xlsx
+++ b/config/excel/DB抽出条件.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silve\EDINET_Pipeline\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687EE20D-23D8-4619-B475-E7F92AA7DD9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B102BE-A0B7-4369-98B1-8F63F9506180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="218">
   <si>
     <t>業種</t>
   </si>
@@ -157,12 +157,6 @@
   <si>
     <t>edinet_monitor
 実行コマンド：</t>
-  </si>
-  <si>
-    <t>$env:PYTHONPATH="C:\Users\silve\EDINET_Pipeline\src"
-.\.venv\Scripts\python.exe -m edinet_monitor.cli.export_metric_excel `
-  --condition-xlsx "C:\Users\silve\EDINET_Pipeline\config\excel\DB抽出条件.xlsx" `
-  --output-dir "D:\作業用"</t>
   </si>
   <si>
     <t>edinet_pipeline
@@ -700,6 +694,17 @@
   --db-path "E:\EDINET_Data\edinet_monitor\db\edinet_monitor.db" `
   --template "C:\Users\silve\EDINET_Pipeline\templates\決算分析シート_1.xlsm" `
   --output-dir "E:\EDINET_Data\edinet_pipeline\output\excel"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4613,7203</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>$env:PYTHONPATH="C:\Users\silve\EDINET_Pipeline\src"
+.\.venv\Scripts\python.exe -m edinet_monitor.cli.export_metric_excel `
+  --condition-xlsx "C:\Users\silve\EDINET_Pipeline\config\excel\DB抽出条件.xlsx" `
+  --output-dir "D:\作業用"</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1031,9 +1036,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1045,6 +1047,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1631,15 +1636,15 @@
       <c r="A2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="33">
-        <v>4613</v>
+      <c r="B2" s="37" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="34"/>
+      <c r="B3" s="33"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="25" t="s">
@@ -1942,15 +1947,15 @@
         <v>38</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>39</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="168.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="35" t="s">
-        <v>216</v>
+        <v>39</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -1978,28 +1983,28 @@
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="F2" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="H2" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="I2" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="L2" s="8"/>
     </row>
@@ -2008,645 +2013,645 @@
         <v>27</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>27</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H3" s="18" t="s">
         <v>27</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L3" s="9"/>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="F4" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="F4" s="22" t="s">
+      <c r="G4" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="G4" s="23" t="s">
-        <v>55</v>
-      </c>
       <c r="H4" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="L4" s="8"/>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="15" t="s">
-        <v>57</v>
-      </c>
       <c r="F5" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="G5" s="23" t="s">
-        <v>53</v>
-      </c>
       <c r="H5" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="L5" s="8"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="F6" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="G6" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="H6" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="H6" s="18" t="s">
+      <c r="I6" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="L6" s="8"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="F7" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="F7" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="H7" s="18" t="s">
+      <c r="I7" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="L7" s="8"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="F8" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="H8" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="F8" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="G8" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="H8" s="18" t="s">
+      <c r="I8" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="L8" s="8"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="F9" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F9" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="H9" s="18" t="s">
+      <c r="I9" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="L9" s="8"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B10" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="D10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="E10" s="15" t="s">
-        <v>85</v>
-      </c>
       <c r="F10" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="G10" s="23" t="s">
-        <v>75</v>
-      </c>
       <c r="H10" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="L10" s="8"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="D11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="E11" s="15" t="s">
-        <v>87</v>
-      </c>
       <c r="F11" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="G11" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="G11" s="23" t="s">
-        <v>81</v>
-      </c>
       <c r="H11" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="L11" s="8"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="D12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="E12" s="15" t="s">
-        <v>89</v>
-      </c>
       <c r="F12" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="G12" s="23" t="s">
-        <v>85</v>
-      </c>
       <c r="H12" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="L12" s="8"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B13" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="D13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E13" s="15" t="s">
-        <v>91</v>
-      </c>
       <c r="F13" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="G13" s="23" t="s">
-        <v>87</v>
-      </c>
       <c r="H13" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="L13" s="8"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="D14" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="E14" s="15" t="s">
-        <v>93</v>
-      </c>
       <c r="F14" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="G14" s="23" t="s">
-        <v>89</v>
-      </c>
       <c r="H14" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="L14" s="8"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="D15" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="E15" s="15" t="s">
-        <v>95</v>
-      </c>
       <c r="F15" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="G15" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="G15" s="23" t="s">
-        <v>91</v>
-      </c>
       <c r="H15" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="L15" s="10"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B16" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="D16" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E16" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="E16" s="15" t="s">
-        <v>97</v>
-      </c>
       <c r="F16" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="G16" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="G16" s="23" t="s">
-        <v>93</v>
-      </c>
       <c r="H16" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="L16" s="8"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B17" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="D17" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E17" s="15" t="s">
-        <v>99</v>
-      </c>
       <c r="F17" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="G17" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="G17" s="23" t="s">
-        <v>95</v>
-      </c>
       <c r="H17" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B18" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="D18" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E18" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E18" s="15" t="s">
-        <v>101</v>
-      </c>
       <c r="F18" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="G18" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="G18" s="23" t="s">
-        <v>97</v>
-      </c>
       <c r="H18" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B19" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="D19" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E19" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="E19" s="15" t="s">
-        <v>103</v>
-      </c>
       <c r="F19" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="G19" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="G19" s="23" t="s">
-        <v>99</v>
-      </c>
       <c r="H19" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="L19" s="8"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B20" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="D20" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E20" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="E20" s="15" t="s">
-        <v>105</v>
-      </c>
       <c r="F20" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="G20" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="G20" s="23" t="s">
-        <v>101</v>
-      </c>
       <c r="H20" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="L20" s="9"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B21" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="D21" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E21" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="E21" s="15" t="s">
-        <v>107</v>
-      </c>
       <c r="F21" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="G21" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="G21" s="23" t="s">
-        <v>103</v>
-      </c>
       <c r="H21" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="L21" s="8"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B22" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="D22" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E22" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="E22" s="15" t="s">
-        <v>109</v>
-      </c>
       <c r="F22" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="G22" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="G22" s="23" t="s">
-        <v>105</v>
-      </c>
       <c r="H22" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="K22" s="11"/>
       <c r="L22" s="12"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B23" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="D23" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E23" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="E23" s="15" t="s">
-        <v>111</v>
-      </c>
       <c r="F23" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="G23" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="G23" s="23" t="s">
-        <v>107</v>
-      </c>
       <c r="H23" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B24" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="D24" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E24" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="E24" s="15" t="s">
-        <v>113</v>
-      </c>
       <c r="F24" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="G24" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="G24" s="23" t="s">
-        <v>109</v>
-      </c>
       <c r="H24" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="L24" s="8"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B25" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F25" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="G25" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="G25" s="23" t="s">
-        <v>111</v>
-      </c>
       <c r="H25" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="K25" s="13"/>
       <c r="L25" s="12"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B26" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>113</v>
-      </c>
       <c r="D26" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="E26" s="15" t="s">
-        <v>116</v>
-      </c>
       <c r="F26" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="G26" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="G26" s="23" t="s">
-        <v>113</v>
-      </c>
       <c r="H26" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="L26" s="8"/>
     </row>
@@ -2655,807 +2660,807 @@
         <v>34</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E27" s="15" t="s">
         <v>117</v>
-      </c>
-      <c r="E27" s="15" t="s">
-        <v>118</v>
       </c>
       <c r="F27" s="22" t="s">
         <v>34</v>
       </c>
       <c r="G27" s="23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H27" s="18" t="s">
         <v>34</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L27" s="8"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B28" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>116</v>
-      </c>
       <c r="D28" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E28" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E28" s="15" t="s">
-        <v>120</v>
-      </c>
       <c r="F28" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="G28" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="G28" s="23" t="s">
-        <v>116</v>
-      </c>
       <c r="H28" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="L28" s="8"/>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B29" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="D29" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E29" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E29" s="15" t="s">
-        <v>122</v>
-      </c>
       <c r="F29" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="G29" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="G29" s="23" t="s">
-        <v>118</v>
-      </c>
       <c r="H29" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B30" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C30" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>120</v>
-      </c>
       <c r="D30" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E30" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E30" s="15" t="s">
-        <v>124</v>
-      </c>
       <c r="F30" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="G30" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="G30" s="23" t="s">
-        <v>120</v>
-      </c>
       <c r="H30" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="L30" s="8"/>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B31" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C31" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>122</v>
-      </c>
       <c r="D31" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E31" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="E31" s="15" t="s">
-        <v>126</v>
-      </c>
       <c r="F31" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="G31" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="G31" s="23" t="s">
-        <v>122</v>
-      </c>
       <c r="H31" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="L31" s="8"/>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B32" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="D32" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E32" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="E32" s="15" t="s">
-        <v>128</v>
-      </c>
       <c r="F32" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="G32" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="G32" s="23" t="s">
-        <v>124</v>
-      </c>
       <c r="H32" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="I32" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="L32" s="8"/>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B33" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C33" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>126</v>
-      </c>
       <c r="D33" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E33" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="E33" s="15" t="s">
-        <v>130</v>
-      </c>
       <c r="F33" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="G33" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="G33" s="23" t="s">
-        <v>126</v>
-      </c>
       <c r="H33" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="I33" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="L33" s="8"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B34" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C34" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>128</v>
-      </c>
       <c r="D34" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E34" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="E34" s="15" t="s">
-        <v>132</v>
-      </c>
       <c r="F34" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="G34" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="G34" s="23" t="s">
-        <v>128</v>
-      </c>
       <c r="H34" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="I34" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B35" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="D35" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E35" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="E35" s="15" t="s">
-        <v>134</v>
-      </c>
       <c r="F35" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G35" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="G35" s="23" t="s">
-        <v>130</v>
-      </c>
       <c r="H35" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="I35" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="L35" s="10"/>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B36" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C36" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>132</v>
-      </c>
       <c r="D36" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E36" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="E36" s="15" t="s">
-        <v>136</v>
-      </c>
       <c r="F36" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="G36" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="G36" s="23" t="s">
-        <v>132</v>
-      </c>
       <c r="H36" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="I36" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="L36" s="8"/>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B37" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C37" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>134</v>
-      </c>
       <c r="D37" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E37" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="E37" s="15" t="s">
-        <v>138</v>
-      </c>
       <c r="F37" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="G37" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="G37" s="23" t="s">
-        <v>134</v>
-      </c>
       <c r="H37" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="I37" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B38" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="D38" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E38" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="E38" s="15" t="s">
-        <v>140</v>
-      </c>
       <c r="F38" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="G38" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="G38" s="23" t="s">
-        <v>136</v>
-      </c>
       <c r="H38" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="I38" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B39" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C39" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="C39" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="D39" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E39" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="E39" s="15" t="s">
-        <v>142</v>
-      </c>
       <c r="F39" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="G39" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="G39" s="23" t="s">
-        <v>138</v>
-      </c>
       <c r="H39" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="I39" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B40" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C40" s="6" t="s">
-        <v>140</v>
-      </c>
       <c r="D40" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E40" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="E40" s="15" t="s">
-        <v>144</v>
-      </c>
       <c r="F40" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="G40" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="G40" s="23" t="s">
-        <v>140</v>
-      </c>
       <c r="H40" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="I40" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B41" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="D41" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E41" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="E41" s="15" t="s">
-        <v>146</v>
-      </c>
       <c r="F41" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="G41" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="G41" s="23" t="s">
-        <v>142</v>
-      </c>
       <c r="H41" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="I41" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B42" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="D42" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E42" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="E42" s="15" t="s">
-        <v>148</v>
-      </c>
       <c r="F42" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="G42" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="G42" s="23" t="s">
-        <v>144</v>
-      </c>
       <c r="H42" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="I42" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B43" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="D43" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E43" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="E43" s="15" t="s">
-        <v>150</v>
-      </c>
       <c r="F43" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="G43" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="G43" s="23" t="s">
-        <v>146</v>
-      </c>
       <c r="H43" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="I43" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B44" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>148</v>
-      </c>
       <c r="D44" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E44" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="E44" s="15" t="s">
-        <v>152</v>
-      </c>
       <c r="F44" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G44" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="G44" s="23" t="s">
-        <v>148</v>
-      </c>
       <c r="H44" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="I44" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B45" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>150</v>
-      </c>
       <c r="D45" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E45" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="E45" s="15" t="s">
-        <v>154</v>
-      </c>
       <c r="F45" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="G45" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="G45" s="23" t="s">
-        <v>150</v>
-      </c>
       <c r="H45" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="I45" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B46" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>152</v>
-      </c>
       <c r="D46" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E46" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="E46" s="15" t="s">
-        <v>156</v>
-      </c>
       <c r="F46" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="G46" s="23" t="s">
         <v>151</v>
       </c>
-      <c r="G46" s="23" t="s">
-        <v>152</v>
-      </c>
       <c r="H46" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="I46" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B47" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>154</v>
-      </c>
       <c r="D47" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E47" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="E47" s="15" t="s">
-        <v>158</v>
-      </c>
       <c r="F47" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G47" s="23" t="s">
         <v>153</v>
       </c>
-      <c r="G47" s="23" t="s">
-        <v>154</v>
-      </c>
       <c r="H47" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="I47" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B48" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="D48" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E48" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="E48" s="15" t="s">
-        <v>160</v>
-      </c>
       <c r="F48" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G48" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="G48" s="23" t="s">
-        <v>156</v>
-      </c>
       <c r="H48" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="I48" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B49" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>158</v>
-      </c>
       <c r="D49" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E49" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="E49" s="15" t="s">
-        <v>162</v>
-      </c>
       <c r="F49" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="G49" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="G49" s="23" t="s">
-        <v>158</v>
-      </c>
       <c r="H49" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="I49" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B50" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C50" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="C50" s="6" t="s">
-        <v>160</v>
-      </c>
       <c r="D50" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E50" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="E50" s="15" t="s">
-        <v>164</v>
-      </c>
       <c r="F50" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="G50" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="G50" s="23" t="s">
-        <v>160</v>
-      </c>
       <c r="H50" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="I50" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B51" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C51" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C51" s="6" t="s">
-        <v>162</v>
-      </c>
       <c r="D51" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E51" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="E51" s="15" t="s">
-        <v>166</v>
-      </c>
       <c r="F51" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="G51" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="G51" s="23" t="s">
-        <v>162</v>
-      </c>
       <c r="H51" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="I51" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B52" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="D52" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E52" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="E52" s="15" t="s">
-        <v>168</v>
-      </c>
       <c r="F52" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="G52" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="G52" s="23" t="s">
-        <v>164</v>
-      </c>
       <c r="H52" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="I52" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B53" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>166</v>
-      </c>
       <c r="D53" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E53" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="E53" s="15" t="s">
-        <v>170</v>
-      </c>
       <c r="F53" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="G53" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="G53" s="23" t="s">
-        <v>166</v>
-      </c>
       <c r="H53" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="I53" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B54" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F54" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="G54" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="G54" s="23" t="s">
-        <v>168</v>
-      </c>
       <c r="H54" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="I54" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B55" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F55" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="G55" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="G55" s="23" t="s">
-        <v>170</v>
-      </c>
       <c r="H55" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="I55" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B56" s="4"/>
       <c r="C56" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F56" s="24"/>
       <c r="G56" s="23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H56" s="19"/>
       <c r="I56" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B57" s="5"/>
       <c r="C57" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="16"/>
       <c r="F57" s="24"/>
       <c r="G57" s="23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H57" s="19"/>
       <c r="I57" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B58" s="5"/>
       <c r="C58" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="16"/>
       <c r="F58" s="24"/>
       <c r="G58" s="23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H58" s="19"/>
       <c r="I58" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -3474,7 +3479,7 @@
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B1" s="27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="2:2" x14ac:dyDescent="0.4">
@@ -3484,172 +3489,172 @@
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B3" s="26" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B4" s="26" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B5" s="26" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B6" s="26" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B7" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B8" s="26" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B9" s="26" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B10" s="26" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B11" s="26" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B12" s="26" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B13" s="26" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B14" s="26" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B15" s="26" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B16" s="26" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B17" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B18" s="26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B19" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B20" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B21" s="26" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B22" s="26" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B23" s="26" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B24" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B25" s="26" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B26" s="26" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B27" s="26" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B28" s="26" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B29" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B30" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B31" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B32" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B33" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B34" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B35" s="26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B36" s="32" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -3668,21 +3673,21 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" s="28" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="B2" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="C2" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="D2" s="29" t="s">
         <v>212</v>
-      </c>
-      <c r="D2" s="29" t="s">
-        <v>213</v>
       </c>
       <c r="E2" s="29" t="s">
         <v>24</v>
@@ -3691,18 +3696,18 @@
         <v>4</v>
       </c>
       <c r="G2" s="29" t="s">
+        <v>213</v>
+      </c>
+      <c r="H2" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="H2" s="29" t="s">
-        <v>215</v>
-      </c>
-      <c r="I2" s="36" t="s">
+      <c r="I2" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="37" t="s">
+      <c r="J2" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="37"/>
+      <c r="K2" s="36"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/config/excel/DB抽出条件.xlsx
+++ b/config/excel/DB抽出条件.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silve\EDINET_Pipeline\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B102BE-A0B7-4369-98B1-8F63F9506180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CA274F-BA45-47F7-8754-ABD9C81154AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -697,14 +697,14 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>4613,7203</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>$env:PYTHONPATH="C:\Users\silve\EDINET_Pipeline\src"
 .\.venv\Scripts\python.exe -m edinet_monitor.cli.export_metric_excel `
   --condition-xlsx "C:\Users\silve\EDINET_Pipeline\config\excel\DB抽出条件.xlsx" `
   --output-dir "D:\作業用"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7203</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1637,7 +1637,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
@@ -1947,7 +1947,7 @@
         <v>38</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="168.75" customHeight="1" x14ac:dyDescent="0.4">

--- a/config/excel/DB抽出条件.xlsx
+++ b/config/excel/DB抽出条件.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silve\EDINET_Pipeline\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CA274F-BA45-47F7-8754-ABD9C81154AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F2E9A5-EDF5-47B7-8FDD-A35C8A4653A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="219">
   <si>
     <t>業種</t>
   </si>
@@ -704,7 +704,17 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>7203</t>
+    <t>10期前</t>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8473,6857,7751,6758,7203,9983,8001,4613</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -952,7 +962,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1024,9 +1034,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1041,9 +1048,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1630,28 +1634,28 @@
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
+      <c r="B1" s="30"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="37" t="s">
-        <v>217</v>
+      <c r="B2" s="35" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="33"/>
+      <c r="B3" s="32"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="25" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>4</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
@@ -1731,6 +1735,7 @@
       <c r="B16" s="26"/>
     </row>
   </sheetData>
+  <dataConsolidate/>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="B6" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -1741,6 +1746,18 @@
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5002AD5A-8807-4C68-A9C1-1E9ADA5E3F75}">
+          <x14:formula1>
+            <xm:f>期間系選択肢!$A$2:$K$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>B4 B5</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -1954,7 +1971,7 @@
       <c r="B3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="33" t="s">
         <v>215</v>
       </c>
     </row>
@@ -3653,7 +3670,7 @@
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B36" s="32" t="s">
+      <c r="B36" s="31" t="s">
         <v>207</v>
       </c>
     </row>
@@ -3677,37 +3694,39 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B2" s="34" t="s">
         <v>209</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="C2" s="34" t="s">
         <v>210</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="D2" s="34" t="s">
         <v>211</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="E2" s="34" t="s">
         <v>212</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="F2" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="G2" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="H2" s="34" t="s">
         <v>213</v>
       </c>
-      <c r="H2" s="29" t="s">
+      <c r="I2" s="34" t="s">
         <v>214</v>
       </c>
-      <c r="I2" s="35" t="s">
+      <c r="J2" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="36" t="s">
+      <c r="K2" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="36"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/config/excel/DB抽出条件.xlsx
+++ b/config/excel/DB抽出条件.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silve\EDINET_Pipeline\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F2E9A5-EDF5-47B7-8FDD-A35C8A4653A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CAFAFDD-4B8A-4A50-8510-279A6BCBD9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="実行コマンド" sheetId="3" r:id="rId3"/>
     <sheet name="指標一覧" sheetId="4" r:id="rId4"/>
     <sheet name="33業種" sheetId="5" r:id="rId5"/>
-    <sheet name="期間系選択肢" sheetId="6" r:id="rId6"/>
+    <sheet name="選択肢" sheetId="6" r:id="rId6"/>
     <sheet name="原本" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="225">
   <si>
     <t>業種</t>
   </si>
@@ -717,12 +717,44 @@
     <t>8473,6857,7751,6758,7203,9983,8001,4613</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>セグメント選択肢</t>
+    <rPh sb="5" eb="8">
+      <t>センタクシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>ALL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>地域</t>
+    <rPh sb="0" eb="2">
+      <t>チイキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セグメント</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -778,8 +810,14 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -808,8 +846,14 @@
         <fgColor rgb="FFD9EAF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -953,6 +997,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -962,7 +1017,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1033,7 +1088,6 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1054,6 +1108,10 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1275,8 +1333,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="テーブル3" displayName="テーブル3" ref="A1:A15" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
-  <autoFilter ref="A1:A15" xr:uid="{00000000-0009-0000-0100-000001000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="テーブル3" displayName="テーブル3" ref="A1:A16" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
+  <autoFilter ref="A1:A16" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
@@ -1622,35 +1680,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="24" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36" style="7" customWidth="1"/>
     <col min="3" max="3" width="42" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" s="29" t="s">
+      <c r="B1" s="29"/>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="34" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="32"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B3" s="31"/>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="25" t="s">
         <v>3</v>
       </c>
@@ -1658,7 +1716,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2">
       <c r="A5" s="25" t="s">
         <v>5</v>
       </c>
@@ -1666,79 +1724,87 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" s="25" t="s">
+    <row r="6" spans="1:2">
+      <c r="A6" s="36" t="s">
+        <v>224</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B7" s="26" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" s="25" t="s">
+    <row r="8" spans="1:2">
+      <c r="A8" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="26"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A8" s="25" t="s">
+      <c r="B8" s="26"/>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="26"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" s="25" t="s">
+      <c r="B9" s="26"/>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="26"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A10" s="25" t="s">
+      <c r="B10" s="26"/>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="26"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A11" s="25" t="s">
+      <c r="B11" s="26"/>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="26"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A12" s="25" t="s">
+      <c r="B12" s="26"/>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="26"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A13" s="25" t="s">
+      <c r="B13" s="26"/>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="26"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A14" s="25" t="s">
+      <c r="B14" s="26"/>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="26"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A15" s="25" t="s">
+      <c r="B15" s="26"/>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="26"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A16" s="25" t="s">
+      <c r="B16" s="26"/>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="26"/>
+      <c r="B17" s="26"/>
     </row>
   </sheetData>
   <dataConsolidate/>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="B6" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B7" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"none,increase,decrease"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1748,12 +1814,18 @@
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5002AD5A-8807-4C68-A9C1-1E9ADA5E3F75}">
           <x14:formula1>
-            <xm:f>期間系選択肢!$A$2:$K$2</xm:f>
+            <xm:f>選択肢!$A$2:$K$2</xm:f>
           </x14:formula1>
           <xm:sqref>B4 B5</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{39D67696-340C-40E0-876B-CAC2C65221BF}">
+          <x14:formula1>
+            <xm:f>選択肢!$A$5:$C$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>B6</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1764,14 +1836,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="24" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -1782,7 +1854,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1793,7 +1865,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1802,7 +1874,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3">
       <c r="A4" s="25" t="s">
         <v>3</v>
       </c>
@@ -1813,7 +1885,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3">
       <c r="A5" s="25" t="s">
         <v>5</v>
       </c>
@@ -1824,7 +1896,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3">
       <c r="A6" s="25" t="s">
         <v>7</v>
       </c>
@@ -1835,7 +1907,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3">
       <c r="A7" s="25" t="s">
         <v>9</v>
       </c>
@@ -1846,7 +1918,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3">
       <c r="A8" s="25" t="s">
         <v>10</v>
       </c>
@@ -1857,7 +1929,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3">
       <c r="A9" s="25" t="s">
         <v>11</v>
       </c>
@@ -1868,7 +1940,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3">
       <c r="A10" s="25" t="s">
         <v>12</v>
       </c>
@@ -1879,7 +1951,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3">
       <c r="A11" s="25" t="s">
         <v>13</v>
       </c>
@@ -1888,7 +1960,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3">
       <c r="A12" s="25" t="s">
         <v>14</v>
       </c>
@@ -1899,7 +1971,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3">
       <c r="A13" s="25" t="s">
         <v>15</v>
       </c>
@@ -1910,7 +1982,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3">
       <c r="A14" s="25" t="s">
         <v>16</v>
       </c>
@@ -1921,7 +1993,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3">
       <c r="A15" s="25" t="s">
         <v>17</v>
       </c>
@@ -1932,7 +2004,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3">
       <c r="A16" s="25" t="s">
         <v>18</v>
       </c>
@@ -1953,13 +2025,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="19.75" style="7" customWidth="1"/>
     <col min="3" max="3" width="68.5" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="93.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:3" ht="93.75" customHeight="1">
       <c r="B2" s="3" t="s">
         <v>38</v>
       </c>
@@ -1967,11 +2039,11 @@
         <v>216</v>
       </c>
     </row>
-    <row r="3" spans="2:3" ht="168.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:3" ht="168.75" customHeight="1">
       <c r="B3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="32" t="s">
         <v>215</v>
       </c>
     </row>
@@ -1984,7 +2056,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:L58"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="24.75" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32" style="7" bestFit="1" customWidth="1"/>
@@ -1998,7 +2070,7 @@
     <col min="12" max="12" width="25" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:12">
       <c r="B2" s="1" t="s">
         <v>40</v>
       </c>
@@ -2025,7 +2097,7 @@
       </c>
       <c r="L2" s="8"/>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:12">
       <c r="B3" s="2" t="s">
         <v>27</v>
       </c>
@@ -2052,7 +2124,7 @@
       </c>
       <c r="L3" s="9"/>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:12">
       <c r="B4" s="2" t="s">
         <v>49</v>
       </c>
@@ -2079,7 +2151,7 @@
       </c>
       <c r="L4" s="8"/>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:12">
       <c r="B5" s="2" t="s">
         <v>51</v>
       </c>
@@ -2106,7 +2178,7 @@
       </c>
       <c r="L5" s="8"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:12">
       <c r="B6" s="2" t="s">
         <v>57</v>
       </c>
@@ -2133,7 +2205,7 @@
       </c>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:12">
       <c r="B7" s="2" t="s">
         <v>65</v>
       </c>
@@ -2160,7 +2232,7 @@
       </c>
       <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:12">
       <c r="B8" s="2" t="s">
         <v>71</v>
       </c>
@@ -2187,7 +2259,7 @@
       </c>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:12">
       <c r="B9" s="2" t="s">
         <v>77</v>
       </c>
@@ -2214,7 +2286,7 @@
       </c>
       <c r="L9" s="8"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:12">
       <c r="B10" s="2" t="s">
         <v>73</v>
       </c>
@@ -2241,7 +2313,7 @@
       </c>
       <c r="L10" s="8"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:12">
       <c r="B11" s="2" t="s">
         <v>79</v>
       </c>
@@ -2268,7 +2340,7 @@
       </c>
       <c r="L11" s="8"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:12">
       <c r="B12" s="2" t="s">
         <v>83</v>
       </c>
@@ -2295,7 +2367,7 @@
       </c>
       <c r="L12" s="8"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:12">
       <c r="B13" s="2" t="s">
         <v>85</v>
       </c>
@@ -2322,7 +2394,7 @@
       </c>
       <c r="L13" s="8"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:12">
       <c r="B14" s="2" t="s">
         <v>87</v>
       </c>
@@ -2349,7 +2421,7 @@
       </c>
       <c r="L14" s="8"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:12">
       <c r="B15" s="2" t="s">
         <v>89</v>
       </c>
@@ -2376,7 +2448,7 @@
       </c>
       <c r="L15" s="10"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:12">
       <c r="B16" s="2" t="s">
         <v>91</v>
       </c>
@@ -2403,7 +2475,7 @@
       </c>
       <c r="L16" s="8"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:12">
       <c r="B17" s="2" t="s">
         <v>93</v>
       </c>
@@ -2429,7 +2501,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:12">
       <c r="B18" s="2" t="s">
         <v>95</v>
       </c>
@@ -2455,7 +2527,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:12">
       <c r="B19" s="2" t="s">
         <v>97</v>
       </c>
@@ -2482,7 +2554,7 @@
       </c>
       <c r="L19" s="8"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:12">
       <c r="B20" s="2" t="s">
         <v>99</v>
       </c>
@@ -2509,7 +2581,7 @@
       </c>
       <c r="L20" s="9"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:12">
       <c r="B21" s="2" t="s">
         <v>101</v>
       </c>
@@ -2536,7 +2608,7 @@
       </c>
       <c r="L21" s="8"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:12">
       <c r="B22" s="2" t="s">
         <v>103</v>
       </c>
@@ -2564,7 +2636,7 @@
       <c r="K22" s="11"/>
       <c r="L22" s="12"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:12">
       <c r="B23" s="2" t="s">
         <v>105</v>
       </c>
@@ -2590,7 +2662,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:12">
       <c r="B24" s="2" t="s">
         <v>107</v>
       </c>
@@ -2617,7 +2689,7 @@
       </c>
       <c r="L24" s="8"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:12">
       <c r="B25" s="2" t="s">
         <v>109</v>
       </c>
@@ -2645,7 +2717,7 @@
       <c r="K25" s="13"/>
       <c r="L25" s="12"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:12">
       <c r="B26" s="2" t="s">
         <v>111</v>
       </c>
@@ -2672,7 +2744,7 @@
       </c>
       <c r="L26" s="8"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:12">
       <c r="B27" s="2" t="s">
         <v>34</v>
       </c>
@@ -2699,7 +2771,7 @@
       </c>
       <c r="L27" s="8"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:12">
       <c r="B28" s="2" t="s">
         <v>114</v>
       </c>
@@ -2726,7 +2798,7 @@
       </c>
       <c r="L28" s="8"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:12">
       <c r="B29" s="2" t="s">
         <v>116</v>
       </c>
@@ -2752,7 +2824,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:12">
       <c r="B30" s="2" t="s">
         <v>118</v>
       </c>
@@ -2779,7 +2851,7 @@
       </c>
       <c r="L30" s="8"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:12">
       <c r="B31" s="2" t="s">
         <v>120</v>
       </c>
@@ -2806,7 +2878,7 @@
       </c>
       <c r="L31" s="8"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:12">
       <c r="B32" s="2" t="s">
         <v>122</v>
       </c>
@@ -2833,7 +2905,7 @@
       </c>
       <c r="L32" s="8"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:12">
       <c r="B33" s="2" t="s">
         <v>124</v>
       </c>
@@ -2860,7 +2932,7 @@
       </c>
       <c r="L33" s="8"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:12">
       <c r="B34" s="2" t="s">
         <v>126</v>
       </c>
@@ -2886,7 +2958,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:12">
       <c r="B35" s="2" t="s">
         <v>128</v>
       </c>
@@ -2913,7 +2985,7 @@
       </c>
       <c r="L35" s="10"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:12">
       <c r="B36" s="2" t="s">
         <v>130</v>
       </c>
@@ -2940,7 +3012,7 @@
       </c>
       <c r="L36" s="8"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:12">
       <c r="B37" s="2" t="s">
         <v>132</v>
       </c>
@@ -2966,7 +3038,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:12">
       <c r="B38" s="2" t="s">
         <v>134</v>
       </c>
@@ -2992,7 +3064,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:12">
       <c r="B39" s="2" t="s">
         <v>136</v>
       </c>
@@ -3018,7 +3090,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:12">
       <c r="B40" s="2" t="s">
         <v>138</v>
       </c>
@@ -3044,7 +3116,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:12">
       <c r="B41" s="2" t="s">
         <v>140</v>
       </c>
@@ -3070,7 +3142,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:12">
       <c r="B42" s="2" t="s">
         <v>142</v>
       </c>
@@ -3096,7 +3168,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:12">
       <c r="B43" s="2" t="s">
         <v>144</v>
       </c>
@@ -3122,7 +3194,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:12">
       <c r="B44" s="2" t="s">
         <v>146</v>
       </c>
@@ -3148,7 +3220,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:12">
       <c r="B45" s="2" t="s">
         <v>148</v>
       </c>
@@ -3174,7 +3246,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:12">
       <c r="B46" s="2" t="s">
         <v>150</v>
       </c>
@@ -3200,7 +3272,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:12">
       <c r="B47" s="2" t="s">
         <v>152</v>
       </c>
@@ -3226,7 +3298,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:12">
       <c r="B48" s="2" t="s">
         <v>154</v>
       </c>
@@ -3252,7 +3324,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:9">
       <c r="B49" s="2" t="s">
         <v>156</v>
       </c>
@@ -3278,7 +3350,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:9">
       <c r="B50" s="2" t="s">
         <v>158</v>
       </c>
@@ -3304,7 +3376,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:9">
       <c r="B51" s="2" t="s">
         <v>160</v>
       </c>
@@ -3330,7 +3402,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:9">
       <c r="B52" s="2" t="s">
         <v>162</v>
       </c>
@@ -3356,7 +3428,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:9">
       <c r="B53" s="2" t="s">
         <v>164</v>
       </c>
@@ -3382,7 +3454,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:9">
       <c r="B54" s="2" t="s">
         <v>166</v>
       </c>
@@ -3406,7 +3478,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="55" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:9">
       <c r="B55" s="2" t="s">
         <v>168</v>
       </c>
@@ -3430,7 +3502,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="56" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:9">
       <c r="B56" s="4"/>
       <c r="C56" s="2" t="s">
         <v>170</v>
@@ -3448,7 +3520,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:9">
       <c r="B57" s="5"/>
       <c r="C57" s="2" t="s">
         <v>171</v>
@@ -3464,7 +3536,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:9">
       <c r="B58" s="5"/>
       <c r="C58" s="2" t="s">
         <v>172</v>
@@ -3489,188 +3561,188 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:B36"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="28" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:2">
       <c r="B1" s="27" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:2">
       <c r="B2" s="26" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:2">
       <c r="B3" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:2">
       <c r="B4" s="26" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:2">
       <c r="B5" s="26" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:2">
       <c r="B6" s="26" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:2">
       <c r="B7" s="26" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:2">
       <c r="B8" s="26" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:2">
       <c r="B9" s="26" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:2">
       <c r="B10" s="26" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:2">
       <c r="B11" s="26" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:2">
       <c r="B12" s="26" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:2">
       <c r="B13" s="26" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:2">
       <c r="B14" s="26" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:2">
       <c r="B15" s="26" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:2">
       <c r="B16" s="26" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:2">
       <c r="B17" s="26" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:2">
       <c r="B18" s="26" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:2">
       <c r="B19" s="26" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:2">
       <c r="B20" s="26" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:2">
       <c r="B21" s="26" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:2">
       <c r="B22" s="26" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:2">
       <c r="B23" s="26" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:2">
       <c r="B24" s="26" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:2">
       <c r="B25" s="26" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:2">
       <c r="B26" s="26" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:2">
       <c r="B27" s="26" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:2">
       <c r="B28" s="26" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:2">
       <c r="B29" s="26" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:2">
       <c r="B30" s="26" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:2">
       <c r="B31" s="26" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:2">
       <c r="B32" s="26" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:2">
       <c r="B33" s="26" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:2">
       <c r="B34" s="26" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:2">
       <c r="B35" s="26" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B36" s="31" t="s">
+    <row r="36" spans="2:2">
+      <c r="B36" s="30" t="s">
         <v>207</v>
       </c>
     </row>
@@ -3682,50 +3754,66 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="10" width="10" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" s="35" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="33" t="s">
         <v>209</v>
       </c>
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="33" t="s">
         <v>210</v>
       </c>
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="33" t="s">
         <v>211</v>
       </c>
-      <c r="E2" s="34" t="s">
+      <c r="E2" s="33" t="s">
         <v>212</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="34" t="s">
+      <c r="G2" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="34" t="s">
+      <c r="H2" s="33" t="s">
         <v>213</v>
       </c>
-      <c r="I2" s="34" t="s">
+      <c r="I2" s="33" t="s">
         <v>214</v>
       </c>
-      <c r="J2" s="34" t="s">
+      <c r="J2" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="34" t="s">
+      <c r="K2" s="33" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="7" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -3737,14 +3825,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="24" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -3752,31 +3840,31 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="26"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="26"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2">
       <c r="A4" s="25" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="26"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2">
       <c r="A5" s="25" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="26"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2">
       <c r="A6" s="25" t="s">
         <v>7</v>
       </c>
@@ -3784,61 +3872,61 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2">
       <c r="A7" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="26"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2">
       <c r="A8" s="25" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="26"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2">
       <c r="A9" s="25" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="26"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:2">
       <c r="A10" s="25" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="26"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:2">
       <c r="A11" s="25" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="26"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:2">
       <c r="A12" s="25" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="26"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:2">
       <c r="A13" s="25" t="s">
         <v>15</v>
       </c>
       <c r="B13" s="26"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:2">
       <c r="A14" s="25" t="s">
         <v>16</v>
       </c>
       <c r="B14" s="26"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:2">
       <c r="A15" s="25" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="26"/>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:2">
       <c r="A16" s="25" t="s">
         <v>18</v>
       </c>

--- a/config/excel/DB抽出条件.xlsx
+++ b/config/excel/DB抽出条件.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silve\EDINET_Pipeline\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CAFAFDD-4B8A-4A50-8510-279A6BCBD9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A68CAE6-A7EA-4D8D-B2A2-D1C03BFD4B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/config/excel/DB抽出条件.xlsx
+++ b/config/excel/DB抽出条件.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silve\EDINET_Pipeline\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A68CAE6-A7EA-4D8D-B2A2-D1C03BFD4B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A38C98-FC75-419D-948A-2EF51C6E9C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="条件" sheetId="1" r:id="rId1"/>
-    <sheet name="入力例" sheetId="2" r:id="rId2"/>
-    <sheet name="実行コマンド" sheetId="3" r:id="rId3"/>
-    <sheet name="指標一覧" sheetId="4" r:id="rId4"/>
-    <sheet name="33業種" sheetId="5" r:id="rId5"/>
-    <sheet name="選択肢" sheetId="6" r:id="rId6"/>
-    <sheet name="原本" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId2"/>
+    <sheet name="入力例" sheetId="2" r:id="rId3"/>
+    <sheet name="実行コマンド" sheetId="3" r:id="rId4"/>
+    <sheet name="指標一覧" sheetId="4" r:id="rId5"/>
+    <sheet name="33業種" sheetId="5" r:id="rId6"/>
+    <sheet name="選択肢" sheetId="6" r:id="rId7"/>
+    <sheet name="原本" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="227">
   <si>
     <t>業種</t>
   </si>
@@ -747,6 +748,17 @@
   </si>
   <si>
     <t>セグメント</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7203</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セグメント確認用</t>
+    <rPh sb="5" eb="8">
+      <t>カクニンヨウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1699,7 +1711,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1834,6 +1846,33 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3DBB0E1-0D61-4A3D-BA0C-84B9381D68A8}">
+  <dimension ref="B1:C2"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="2" max="2" width="11.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:3">
+      <c r="B1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="2" spans="2:3">
+      <c r="B2" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>218</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -2022,7 +2061,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:C3"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -2053,7 +2092,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:L58"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -3558,7 +3597,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:B36"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -3752,7 +3791,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -3822,7 +3861,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="18.75"/>

--- a/config/excel/DB抽出条件.xlsx
+++ b/config/excel/DB抽出条件.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silve\EDINET_Pipeline\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A38C98-FC75-419D-948A-2EF51C6E9C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217D6260-EC1C-4D69-8400-275170DE5CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="226">
   <si>
     <t>業種</t>
   </si>
@@ -748,10 +748,6 @@
   </si>
   <si>
     <t>セグメント</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>7203</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1711,7 +1707,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1855,7 +1851,7 @@
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" spans="2:3">

--- a/config/excel/DB抽出条件.xlsx
+++ b/config/excel/DB抽出条件.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silve\EDINET_Pipeline\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217D6260-EC1C-4D69-8400-275170DE5CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9700F8-5527-4787-9671-D34DC28776CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/config/excel/DB抽出条件.xlsx
+++ b/config/excel/DB抽出条件.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silve\EDINET_Pipeline\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9700F8-5527-4787-9671-D34DC28776CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E0836E7-261F-4AB8-8E02-8C5BA349873F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="228">
   <si>
     <t>業種</t>
   </si>
@@ -755,6 +755,23 @@
     <rPh sb="5" eb="8">
       <t>カクニンヨウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>銀行、証券、商品先物取引業、保険業用</t>
+    <rPh sb="0" eb="2">
+      <t>ギンコウ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>ホケンギョウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8355, 7182, 8473, 8253, 8766</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1843,7 +1860,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3DBB0E1-0D61-4A3D-BA0C-84B9381D68A8}">
-  <dimension ref="B1:C2"/>
+  <dimension ref="B1:C4"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="11.25" bestFit="1" customWidth="1"/>
@@ -1860,6 +1877,19 @@
       </c>
       <c r="C2" s="34" t="s">
         <v>218</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3">
+      <c r="B3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3">
+      <c r="B4" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/config/excel/DB抽出条件.xlsx
+++ b/config/excel/DB抽出条件.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silve\EDINET_Pipeline\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E0836E7-261F-4AB8-8E02-8C5BA349873F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84BEB66C-D162-4095-821F-8C406029550F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="232">
   <si>
     <t>業種</t>
   </si>
@@ -772,6 +772,37 @@
   </si>
   <si>
     <t>8355, 7182, 8473, 8253, 8766</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通常監査セット</t>
+    <rPh sb="0" eb="2">
+      <t>ツウジョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1928,2914,5889,1844,3636,6454,3391,8601,9501,9743</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>既知異常検知セット</t>
+    <rPh sb="0" eb="2">
+      <t>キチ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケンチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8209,2978,6195,7203,8267,9984</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1724,7 +1755,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1860,7 +1891,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3DBB0E1-0D61-4A3D-BA0C-84B9381D68A8}">
-  <dimension ref="B1:C4"/>
+  <dimension ref="B1:C8"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="11.25" bestFit="1" customWidth="1"/>
@@ -1890,6 +1921,32 @@
       </c>
       <c r="C4" s="34" t="s">
         <v>227</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
+      <c r="B5" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="B6" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
+      <c r="B7" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
+      <c r="B8" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>231</v>
       </c>
     </row>
   </sheetData>

--- a/config/excel/DB抽出条件.xlsx
+++ b/config/excel/DB抽出条件.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silve\EDINET_Pipeline\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84BEB66C-D162-4095-821F-8C406029550F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53932A41-6E2B-4185-8630-FCF313C0AC4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1755,7 +1755,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:2">

--- a/config/excel/DB抽出条件.xlsx
+++ b/config/excel/DB抽出条件.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silve\EDINET_Pipeline\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53932A41-6E2B-4185-8630-FCF313C0AC4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F6280F0-8D6D-4F06-882A-6886B5D0503C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1744,27 +1744,28 @@
     <col min="3" max="3" width="42" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="29"/>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:3">
       <c r="A2" s="28" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>218</v>
+      </c>
+      <c r="C2"/>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="31"/>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:3">
       <c r="A4" s="25" t="s">
         <v>3</v>
       </c>
@@ -1772,7 +1773,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:3">
       <c r="A5" s="25" t="s">
         <v>5</v>
       </c>
@@ -1780,7 +1781,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:3">
       <c r="A6" s="36" t="s">
         <v>224</v>
       </c>
@@ -1788,7 +1789,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:3">
       <c r="A7" s="25" t="s">
         <v>7</v>
       </c>
@@ -1796,55 +1797,55 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:3">
       <c r="A8" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="26"/>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:3">
       <c r="A9" s="25" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="26"/>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:3">
       <c r="A10" s="25" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="26"/>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:3">
       <c r="A11" s="25" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="26"/>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:3">
       <c r="A12" s="25" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="26"/>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:3">
       <c r="A13" s="25" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="26"/>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:3">
       <c r="A14" s="25" t="s">
         <v>15</v>
       </c>
       <c r="B14" s="26"/>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:3">
       <c r="A15" s="25" t="s">
         <v>16</v>
       </c>
       <c r="B15" s="26"/>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:3">
       <c r="A16" s="25" t="s">
         <v>17</v>
       </c>

--- a/config/excel/DB抽出条件.xlsx
+++ b/config/excel/DB抽出条件.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silve\EDINET_Pipeline\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F6280F0-8D6D-4F06-882A-6886B5D0503C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E965756-F8AA-4302-8B96-A7255C3153B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1755,7 +1755,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="C2"/>
     </row>

--- a/config/excel/DB抽出条件.xlsx
+++ b/config/excel/DB抽出条件.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silve\EDINET_Pipeline\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E965756-F8AA-4302-8B96-A7255C3153B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83EBD3C7-DB47-479D-98B9-687486CB7B09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1755,7 +1755,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="C2"/>
     </row>

--- a/config/excel/DB抽出条件.xlsx
+++ b/config/excel/DB抽出条件.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silve\EDINET_Pipeline\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83EBD3C7-DB47-479D-98B9-687486CB7B09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDFC70BB-152D-449C-9154-6716864DDEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1770,7 +1770,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:3">

--- a/config/excel/DB抽出条件.xlsx
+++ b/config/excel/DB抽出条件.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silve\EDINET_Pipeline\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDFC70BB-152D-449C-9154-6716864DDEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D831D0DD-0F3B-41AE-A599-81CF4CF89891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1755,7 +1755,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="C2"/>
     </row>
@@ -1770,7 +1770,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:3">

--- a/config/excel/DB抽出条件.xlsx
+++ b/config/excel/DB抽出条件.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silve\EDINET_Pipeline\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D831D0DD-0F3B-41AE-A599-81CF4CF89891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C76B666-974C-4F1D-9B51-F531B33D7289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/config/excel/DB抽出条件.xlsx
+++ b/config/excel/DB抽出条件.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silve\EDINET_Pipeline\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C76B666-974C-4F1D-9B51-F531B33D7289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{842687AE-A057-481A-A91E-EA3AFBC7072D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1770,7 +1770,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1778,7 +1778,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:3">

--- a/config/excel/DB抽出条件.xlsx
+++ b/config/excel/DB抽出条件.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silve\EDINET_Pipeline\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{842687AE-A057-481A-A91E-EA3AFBC7072D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D091ECF-2376-4F69-B7F8-8C9EEA07AE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="233">
   <si>
     <t>業種</t>
   </si>
@@ -803,6 +803,10 @@
   </si>
   <si>
     <t>8209,2978,6195,7203,8267,9984</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前期</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1755,7 +1759,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C2"/>
     </row>
@@ -1778,7 +1782,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>29</v>
+        <v>232</v>
       </c>
     </row>
     <row r="6" spans="1:3">
